--- a/template_bang_cong.xlsx
+++ b/template_bang_cong.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/htdocs/Cham_cong_Ngay_phep_Ngoai_gio/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lequocvan/Downloads/Cham_cong_Ngoai_gio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B9E3D33-C14F-064F-ACBD-4312C5B678F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9A9C790-ECB8-F74E-A3A2-B6C9CD17A17A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="360" yWindow="460" windowWidth="25240" windowHeight="9320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>Mã NV</t>
   </si>
@@ -130,9 +130,6 @@
     <t>Và Phát triển nông thôn Việt Nam</t>
   </si>
   <si>
-    <t>Trung tâm PCRT</t>
-  </si>
-  <si>
     <t>BẢNG CHẤM CÔNG</t>
   </si>
   <si>
@@ -143,6 +140,12 @@
   </si>
   <si>
     <t>Ngày Ăn Ca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đơn vị: </t>
+  </si>
+  <si>
+    <t>Phòng:</t>
   </si>
 </sst>
 </file>
@@ -201,13 +204,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -217,9 +217,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -543,178 +540,178 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
     </row>
     <row r="2" spans="1:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
-      <c r="V2" s="7"/>
-      <c r="W2" s="7"/>
-      <c r="X2" s="7"/>
-      <c r="Y2" s="7"/>
-      <c r="Z2" s="7"/>
-      <c r="AA2" s="7"/>
-      <c r="AB2" s="7"/>
-      <c r="AC2" s="7"/>
-      <c r="AD2" s="7"/>
-      <c r="AE2" s="7"/>
-      <c r="AF2" s="7"/>
-      <c r="AG2" s="7"/>
-      <c r="AH2" s="7"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="5"/>
+      <c r="AA2" s="5"/>
+      <c r="AB2" s="5"/>
+      <c r="AC2" s="5"/>
+      <c r="AD2" s="5"/>
+      <c r="AE2" s="5"/>
+      <c r="AF2" s="5"/>
+      <c r="AG2" s="5"/>
+      <c r="AH2" s="5"/>
     </row>
     <row r="3" spans="1:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
+      <c r="A3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
     </row>
     <row r="4" spans="1:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
+      <c r="A4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
     </row>
     <row r="5" spans="1:37" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="6" spans="1:37" ht="64" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="J6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="K6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L6" s="3" t="s">
+      <c r="L6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M6" s="3" t="s">
+      <c r="M6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N6" s="3" t="s">
+      <c r="N6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O6" s="3" t="s">
+      <c r="O6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P6" s="3" t="s">
+      <c r="P6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q6" s="3" t="s">
+      <c r="Q6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R6" s="3" t="s">
+      <c r="R6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S6" s="3" t="s">
+      <c r="S6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T6" s="3" t="s">
+      <c r="T6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U6" s="3" t="s">
+      <c r="U6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V6" s="3" t="s">
+      <c r="V6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W6" s="3" t="s">
+      <c r="W6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X6" s="3" t="s">
+      <c r="X6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y6" s="3" t="s">
+      <c r="Y6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z6" s="3" t="s">
+      <c r="Z6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA6" s="3" t="s">
+      <c r="AA6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB6" s="3" t="s">
+      <c r="AB6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AC6" s="3" t="s">
+      <c r="AC6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AD6" s="3" t="s">
+      <c r="AD6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AE6" s="3" t="s">
+      <c r="AE6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AF6" s="3" t="s">
+      <c r="AF6" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AG6" s="3" t="s">
+      <c r="AG6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AH6" s="3" t="s">
+      <c r="AH6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AI6" s="4" t="s">
+      <c r="AI6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="AJ6" s="4" t="s">
+      <c r="AK6" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="AK6" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -722,8 +719,8 @@
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="D2:AH2"/>
+    <mergeCell ref="A4:C4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
